--- a/artfynd/A 62738-2025 artfynd.xlsx
+++ b/artfynd/A 62738-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127012709</v>
       </c>
       <c r="B2" t="n">
-        <v>92622</v>
+        <v>92609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127012698</v>
       </c>
       <c r="B3" t="n">
-        <v>96702</v>
+        <v>96689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127012704</v>
       </c>
       <c r="B4" t="n">
-        <v>90716</v>
+        <v>90703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127012703</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127012707</v>
       </c>
       <c r="B6" t="n">
-        <v>91332</v>
+        <v>91319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127012701</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127012705</v>
       </c>
       <c r="B8" t="n">
-        <v>96702</v>
+        <v>96689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127012708</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127012710</v>
       </c>
       <c r="B10" t="n">
-        <v>79609</v>
+        <v>79600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127012700</v>
       </c>
       <c r="B11" t="n">
-        <v>75127</v>
+        <v>75118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127012702</v>
       </c>
       <c r="B12" t="n">
-        <v>96702</v>
+        <v>96689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 62738-2025 artfynd.xlsx
+++ b/artfynd/A 62738-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127012709</v>
       </c>
       <c r="B2" t="n">
-        <v>92609</v>
+        <v>92622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127012698</v>
       </c>
       <c r="B3" t="n">
-        <v>96689</v>
+        <v>96702</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127012704</v>
       </c>
       <c r="B4" t="n">
-        <v>90703</v>
+        <v>90716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127012703</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127012707</v>
       </c>
       <c r="B6" t="n">
-        <v>91319</v>
+        <v>91332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127012701</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127012705</v>
       </c>
       <c r="B8" t="n">
-        <v>96689</v>
+        <v>96702</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127012708</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127012710</v>
       </c>
       <c r="B10" t="n">
-        <v>79600</v>
+        <v>79609</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127012700</v>
       </c>
       <c r="B11" t="n">
-        <v>75118</v>
+        <v>75127</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127012702</v>
       </c>
       <c r="B12" t="n">
-        <v>96689</v>
+        <v>96702</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 62738-2025 artfynd.xlsx
+++ b/artfynd/A 62738-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127012709</v>
+        <v>127012698</v>
       </c>
       <c r="B2" t="n">
-        <v>92622</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542155</v>
+        <v>542279</v>
       </c>
       <c r="R2" t="n">
-        <v>7000134</v>
+        <v>7000298</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127012698</v>
+        <v>127012702</v>
       </c>
       <c r="B3" t="n">
-        <v>96702</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542279</v>
+        <v>542214</v>
       </c>
       <c r="R3" t="n">
-        <v>7000298</v>
+        <v>7000319</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127012704</v>
+        <v>127012705</v>
       </c>
       <c r="B4" t="n">
-        <v>90716</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5685</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127012703</v>
+        <v>127012707</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542214</v>
+        <v>542193</v>
       </c>
       <c r="R5" t="n">
-        <v>7000319</v>
+        <v>7000249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127012707</v>
+        <v>127012709</v>
       </c>
       <c r="B6" t="n">
-        <v>91332</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542193</v>
+        <v>542155</v>
       </c>
       <c r="R6" t="n">
-        <v>7000249</v>
+        <v>7000134</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127012701</v>
+        <v>127012704</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>91282</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542242</v>
+        <v>542197</v>
       </c>
       <c r="R7" t="n">
-        <v>7000330</v>
+        <v>7000273</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127012705</v>
+        <v>127012701</v>
       </c>
       <c r="B8" t="n">
-        <v>96702</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542197</v>
+        <v>542242</v>
       </c>
       <c r="R8" t="n">
-        <v>7000273</v>
+        <v>7000330</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,11 +1357,11 @@
         <v>127012708</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127012710</v>
+        <v>127012700</v>
       </c>
       <c r="B10" t="n">
-        <v>79609</v>
+        <v>83290</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6439</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542149</v>
+        <v>542268</v>
       </c>
       <c r="R10" t="n">
-        <v>7000153</v>
+        <v>7000306</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127012700</v>
+        <v>127012703</v>
       </c>
       <c r="B11" t="n">
-        <v>75127</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542268</v>
+        <v>542214</v>
       </c>
       <c r="R11" t="n">
-        <v>7000306</v>
+        <v>7000319</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127012702</v>
+        <v>127012710</v>
       </c>
       <c r="B12" t="n">
-        <v>96702</v>
+        <v>79917</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542214</v>
+        <v>542149</v>
       </c>
       <c r="R12" t="n">
-        <v>7000319</v>
+        <v>7000153</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 62738-2025 artfynd.xlsx
+++ b/artfynd/A 62738-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127012698</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127012702</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127012705</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127012707</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127012709</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127012704</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127012701</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127012708</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127012700</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127012703</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,8 +1794,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127012710</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>